--- a/plugins/inbound-cph/skills/responsive-search-ads/template.xlsx
+++ b/plugins/inbound-cph/skills/responsive-search-ads/template.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,8 @@
     <col width="6" customWidth="1" min="46" max="46"/>
     <col width="18" customWidth="1" min="47" max="47"/>
     <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="18" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -729,6 +731,16 @@
           <t>Final mobile URL</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Vinkel</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Hypotese</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" t="inlineStr">
